--- a/assets/清结算银行账户表.xlsx
+++ b/assets/清结算银行账户表.xlsx
@@ -559,8 +559,8 @@
     <col min="24" max="24" width="24" style="1" customWidth="1"/>
     <col min="25" max="25" width="16" customWidth="1"/>
     <col min="26" max="26" width="14" customWidth="1"/>
-    <col min="27" max="29" width="14" style="1" customWidth="1"/>
-    <col min="30" max="32" width="14" customWidth="1"/>
+    <col min="27" max="30" width="14" style="1" customWidth="1"/>
+    <col min="31" max="32" width="14" customWidth="1"/>
     <col min="33" max="33" width="14" style="1" customWidth="1"/>
     <col min="34" max="34" width="16" style="1" customWidth="1"/>
     <col min="35" max="39" width="14" customWidth="1"/>
@@ -655,7 +655,7 @@
       <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
